--- a/e_commerce_forms/012_ticket_marketplace_customer_support_contact_request--e_commerce_forms.xlsx
+++ b/e_commerce_forms/012_ticket_marketplace_customer_support_contact_request--e_commerce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,8 +750,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -779,12 +779,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'technical_support',_'value':_'technical_support'}</t>
+          <t>technical_support</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Technical Support', 'value': 'Technical Support'}</t>
+          <t>Technical Support</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'general_inquiries',_'value':_'general_inquiries'}</t>
+          <t>general_inquiries</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'General Inquiries', 'value': 'General Inquiries'}</t>
+          <t>General Inquiries</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'as_soon_as_possible',_'value':_'as_soon_as_possible'}</t>
+          <t>as_soon_as_possible</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'As soon as possible', 'value': 'As soon as possible'}</t>
+          <t>As soon as possible</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'within_a_few_hours',_'value':_'within_a_few_hours'}</t>
+          <t>within_a_few_hours</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Within a few hours', 'value': 'Within a few hours'}</t>
+          <t>Within a few hours</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'later_today',_'value':_'later_today'}</t>
+          <t>later_today</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Later today', 'value': 'Later today'}</t>
+          <t>Later today</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'later_tomorrow',_'value':_'later_tomorrow'}</t>
+          <t>later_tomorrow</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Later tomorrow', 'value': 'Later tomorrow'}</t>
+          <t>Later tomorrow</t>
         </is>
       </c>
     </row>
